--- a/labs/03-copilot-studio/03-advanced/04-reasoning/lab-01-supplier-recommendation/supplier-scorecard.xlsx
+++ b/labs/03-copilot-studio/03-advanced/04-reasoning/lab-01-supplier-recommendation/supplier-scorecard.xlsx
@@ -509,7 +509,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nordwind Botanicals</t>
+          <t>Rhinevale Botanicals</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
